--- a/AAII_Financials/Quarterly/SUNB_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SUNB_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="92">
   <si>
     <t>SUNB</t>
   </si>
@@ -655,143 +655,167 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A5:K102"/>
+  <dimension ref="A5:M102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="13" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46234</v>
+      </c>
+      <c r="E7" s="2">
+        <v>46142</v>
+      </c>
+      <c r="F7" s="2">
         <v>46053</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45961</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45869</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45777</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45688</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45596</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45504</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45412</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>3115000</v>
+      </c>
+      <c r="E8" s="3">
+        <v>2754000</v>
+      </c>
+      <c r="F8" s="3">
         <v>2637000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>2962100</v>
       </c>
-      <c r="F8" s="3">
-        <v>2800900</v>
-      </c>
-      <c r="G8" s="3">
-        <v>2529300</v>
-      </c>
       <c r="H8" s="3">
+        <v>2801000</v>
+      </c>
+      <c r="I8" s="3">
+        <v>2529000</v>
+      </c>
+      <c r="J8" s="3">
         <v>2567000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>2941300</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>2753700</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>2627500</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>1866000</v>
+      </c>
+      <c r="E9" s="3">
+        <v>1772000</v>
+      </c>
+      <c r="F9" s="3">
         <v>1652000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>3318800</v>
       </c>
-      <c r="F9" s="3">
-        <v>90200</v>
-      </c>
-      <c r="G9" s="3">
-        <v>88400</v>
-      </c>
       <c r="H9" s="3">
+        <v>1678000</v>
+      </c>
+      <c r="I9" s="3">
+        <v>1594000</v>
+      </c>
+      <c r="J9" s="3">
         <v>1577000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>3199100</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>100900</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>165400</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>1249000</v>
+      </c>
+      <c r="E10" s="3">
+        <v>982000</v>
+      </c>
+      <c r="F10" s="3">
         <v>985000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>-356700</v>
       </c>
-      <c r="F10" s="3">
-        <v>2710700</v>
-      </c>
-      <c r="G10" s="3">
-        <v>2440900</v>
-      </c>
       <c r="H10" s="3">
+        <v>1123000</v>
+      </c>
+      <c r="I10" s="3">
+        <v>935000</v>
+      </c>
+      <c r="J10" s="3">
         <v>990000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>-257800</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>2652800</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>2462100</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -803,8 +827,10 @@
       <c r="I11" s="3"/>
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L11" s="3"/>
+      <c r="M11" s="3"/>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -832,8 +858,14 @@
       <c r="K12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -861,66 +893,84 @@
       <c r="K13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L13" s="3">
+        <v>0</v>
+      </c>
+      <c r="M13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>6000</v>
+      </c>
+      <c r="E14" s="3">
+        <v>131000</v>
+      </c>
+      <c r="F14" s="3">
         <v>1000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="G14" s="3">
         <v>26300</v>
       </c>
-      <c r="F14" s="3">
-        <v>12700</v>
-      </c>
-      <c r="G14" s="3">
-        <v>-2900</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>8</v>
+      <c r="H14" s="3">
+        <v>13000</v>
       </c>
       <c r="I14" s="3">
+        <v>-27000</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K14" s="3">
         <v>25000</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M14" s="3">
         <v>-16000</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>115000</v>
+      </c>
+      <c r="E15" s="3">
+        <v>115000</v>
+      </c>
+      <c r="F15" s="3">
         <v>113000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="G15" s="3">
         <v>-396400</v>
       </c>
-      <c r="F15" s="3">
-        <v>621400</v>
-      </c>
-      <c r="G15" s="3">
-        <v>614800</v>
-      </c>
       <c r="H15" s="3">
+        <v>113000</v>
+      </c>
+      <c r="I15" s="3">
         <v>111000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
+        <v>111000</v>
+      </c>
+      <c r="K15" s="3">
         <v>-385400</v>
       </c>
-      <c r="J15" s="3">
+      <c r="L15" s="3">
         <v>599400</v>
       </c>
-      <c r="K15" s="3">
+      <c r="M15" s="3">
         <v>573900</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -929,66 +979,80 @@
       <c r="I16" s="3"/>
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
-    </row>
-    <row r="17" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L16" s="3"/>
+      <c r="M16" s="3"/>
+    </row>
+    <row r="17" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>2418000</v>
+      </c>
+      <c r="E17" s="3">
+        <v>2207000</v>
+      </c>
+      <c r="F17" s="3">
         <v>2144000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>2305600</v>
       </c>
-      <c r="F17" s="3">
-        <v>2146400</v>
-      </c>
-      <c r="G17" s="3">
-        <v>2009300</v>
-      </c>
       <c r="H17" s="3">
+        <v>2192000</v>
+      </c>
+      <c r="I17" s="3">
+        <v>1998000</v>
+      </c>
+      <c r="J17" s="3">
         <v>2035000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>2178600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>2065400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>2082100</v>
       </c>
     </row>
-    <row r="18" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>697000</v>
+      </c>
+      <c r="E18" s="3">
+        <v>547000</v>
+      </c>
+      <c r="F18" s="3">
         <v>493000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>656500</v>
       </c>
-      <c r="F18" s="3">
-        <v>654500</v>
-      </c>
-      <c r="G18" s="3">
-        <v>520000</v>
-      </c>
       <c r="H18" s="3">
+        <v>609000</v>
+      </c>
+      <c r="I18" s="3">
+        <v>531000</v>
+      </c>
+      <c r="J18" s="3">
         <v>532000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>762700</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>688300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>545400</v>
       </c>
     </row>
-    <row r="19" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1000,153 +1064,185 @@
       <c r="I19" s="3"/>
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
-    </row>
-    <row r="20" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L19" s="3"/>
+      <c r="M19" s="3"/>
+    </row>
+    <row r="20" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>8</v>
+      <c r="D20" s="3">
+        <v>-7000</v>
       </c>
       <c r="E20" s="3">
+        <v>4000</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G20" s="3">
         <v>-12000</v>
       </c>
-      <c r="F20" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G20" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="H20" s="3">
+        <v>-7000</v>
+      </c>
+      <c r="I20" s="3">
+        <v>35000</v>
+      </c>
+      <c r="J20" s="3">
         <v>-5000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="K20" s="3">
         <v>-9000</v>
       </c>
-      <c r="J20" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K20" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="21" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M20" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="21" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>819000</v>
+      </c>
+      <c r="E21" s="3">
+        <v>658000</v>
+      </c>
+      <c r="F21" s="3">
         <v>606000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>272100</v>
       </c>
-      <c r="F21" s="3">
-        <v>1275900</v>
-      </c>
-      <c r="G21" s="3">
-        <v>1134800</v>
-      </c>
       <c r="H21" s="3">
+        <v>729000</v>
+      </c>
+      <c r="I21" s="3">
+        <v>607000</v>
+      </c>
+      <c r="J21" s="3">
         <v>648000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>386300</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>1287700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>1119300</v>
       </c>
     </row>
-    <row r="22" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>107000</v>
+      </c>
+      <c r="E22" s="3">
+        <v>96000</v>
+      </c>
+      <c r="F22" s="3">
         <v>98000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="G22" s="3">
         <v>61200</v>
       </c>
-      <c r="F22" s="3">
-        <v>131800</v>
-      </c>
-      <c r="G22" s="3">
-        <v>135100</v>
-      </c>
       <c r="H22" s="3">
+        <v>95000</v>
+      </c>
+      <c r="I22" s="3">
+        <v>96000</v>
+      </c>
+      <c r="J22" s="3">
         <v>107000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="K22" s="3">
         <v>78100</v>
       </c>
-      <c r="J22" s="3">
+      <c r="L22" s="3">
         <v>143900</v>
       </c>
-      <c r="K22" s="3">
+      <c r="M22" s="3">
         <v>144400</v>
       </c>
     </row>
-    <row r="23" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>591000</v>
+      </c>
+      <c r="E23" s="3">
+        <v>316000</v>
+      </c>
+      <c r="F23" s="3">
         <v>394000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>579400</v>
       </c>
-      <c r="F23" s="3">
-        <v>511600</v>
-      </c>
-      <c r="G23" s="3">
-        <v>392200</v>
-      </c>
       <c r="H23" s="3">
+        <v>508000</v>
+      </c>
+      <c r="I23" s="3">
+        <v>427000</v>
+      </c>
+      <c r="J23" s="3">
         <v>430000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>668600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>544400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>417000</v>
       </c>
     </row>
-    <row r="24" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>153000</v>
+      </c>
+      <c r="E24" s="3">
+        <v>90000</v>
+      </c>
+      <c r="F24" s="3">
         <v>104000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="G24" s="3">
         <v>145900</v>
       </c>
-      <c r="F24" s="3">
-        <v>136100</v>
-      </c>
-      <c r="G24" s="3">
-        <v>80900</v>
-      </c>
       <c r="H24" s="3">
+        <v>135000</v>
+      </c>
+      <c r="I24" s="3">
+        <v>98000</v>
+      </c>
+      <c r="J24" s="3">
         <v>105000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="K24" s="3">
         <v>173100</v>
       </c>
-      <c r="J24" s="3">
+      <c r="L24" s="3">
         <v>140900</v>
       </c>
-      <c r="K24" s="3">
+      <c r="M24" s="3">
         <v>92300</v>
       </c>
     </row>
-    <row r="25" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1174,66 +1270,84 @@
       <c r="K25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L25" s="3">
+        <v>0</v>
+      </c>
+      <c r="M25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>438000</v>
+      </c>
+      <c r="E26" s="3">
+        <v>226000</v>
+      </c>
+      <c r="F26" s="3">
         <v>290000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>433500</v>
       </c>
-      <c r="F26" s="3">
-        <v>375500</v>
-      </c>
-      <c r="G26" s="3">
-        <v>311300</v>
-      </c>
       <c r="H26" s="3">
+        <v>373000</v>
+      </c>
+      <c r="I26" s="3">
+        <v>329000</v>
+      </c>
+      <c r="J26" s="3">
         <v>325000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>495500</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>403500</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>324700</v>
       </c>
     </row>
-    <row r="27" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>438000</v>
+      </c>
+      <c r="E27" s="3">
+        <v>226000</v>
+      </c>
+      <c r="F27" s="3">
         <v>290000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>433500</v>
       </c>
-      <c r="F27" s="3">
-        <v>375500</v>
-      </c>
-      <c r="G27" s="3">
-        <v>311300</v>
-      </c>
       <c r="H27" s="3">
+        <v>373000</v>
+      </c>
+      <c r="I27" s="3">
+        <v>329000</v>
+      </c>
+      <c r="J27" s="3">
         <v>325000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>495500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>403500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>324700</v>
       </c>
     </row>
-    <row r="28" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1261,8 +1375,14 @@
       <c r="K28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L28" s="3">
+        <v>0</v>
+      </c>
+      <c r="M28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1290,8 +1410,14 @@
       <c r="K29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L29" s="3">
+        <v>0</v>
+      </c>
+      <c r="M29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1319,8 +1445,14 @@
       <c r="K30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L30" s="3">
+        <v>0</v>
+      </c>
+      <c r="M30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1348,66 +1480,84 @@
       <c r="K31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L31" s="3">
+        <v>0</v>
+      </c>
+      <c r="M31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>8</v>
+      <c r="D32" s="3">
+        <v>7000</v>
       </c>
       <c r="E32" s="3">
+        <v>-4000</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G32" s="3">
         <v>12000</v>
       </c>
-      <c r="F32" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G32" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="H32" s="3">
+        <v>7000</v>
+      </c>
+      <c r="I32" s="3">
+        <v>-35000</v>
+      </c>
+      <c r="J32" s="3">
         <v>5000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="K32" s="3">
         <v>9000</v>
       </c>
-      <c r="J32" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K32" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="33" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M32" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="33" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>438000</v>
+      </c>
+      <c r="E33" s="3">
+        <v>226000</v>
+      </c>
+      <c r="F33" s="3">
         <v>290000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>433500</v>
       </c>
-      <c r="F33" s="3">
-        <v>375500</v>
-      </c>
-      <c r="G33" s="3">
-        <v>311300</v>
-      </c>
       <c r="H33" s="3">
+        <v>373000</v>
+      </c>
+      <c r="I33" s="3">
+        <v>329000</v>
+      </c>
+      <c r="J33" s="3">
         <v>325000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>495500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>403500</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>324700</v>
       </c>
     </row>
-    <row r="34" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1435,71 +1585,89 @@
       <c r="K34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L34" s="3">
+        <v>0</v>
+      </c>
+      <c r="M34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>438000</v>
+      </c>
+      <c r="E35" s="3">
+        <v>226000</v>
+      </c>
+      <c r="F35" s="3">
         <v>290000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>433500</v>
       </c>
-      <c r="F35" s="3">
-        <v>375500</v>
-      </c>
-      <c r="G35" s="3">
-        <v>311300</v>
-      </c>
       <c r="H35" s="3">
+        <v>373000</v>
+      </c>
+      <c r="I35" s="3">
+        <v>329000</v>
+      </c>
+      <c r="J35" s="3">
         <v>325000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>495500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>403500</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>324700</v>
       </c>
     </row>
-    <row r="37" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46234</v>
+      </c>
+      <c r="E38" s="2">
+        <v>46142</v>
+      </c>
+      <c r="F38" s="2">
         <v>46053</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45961</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45869</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45777</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45688</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45596</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45504</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45412</v>
       </c>
     </row>
-    <row r="39" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1511,8 +1679,10 @@
       <c r="I39" s="3"/>
       <c r="J39" s="3"/>
       <c r="K39" s="3"/>
-    </row>
-    <row r="40" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L39" s="3"/>
+      <c r="M39" s="3"/>
+    </row>
+    <row r="40" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1524,37 +1694,45 @@
       <c r="I40" s="3"/>
       <c r="J40" s="3"/>
       <c r="K40" s="3"/>
-    </row>
-    <row r="41" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L40" s="3"/>
+      <c r="M40" s="3"/>
+    </row>
+    <row r="41" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>32000</v>
+      </c>
+      <c r="E41" s="3">
+        <v>29000</v>
+      </c>
+      <c r="F41" s="3">
         <v>39000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>39600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>22900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>21000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>25800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>23700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>17000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>20800</v>
       </c>
     </row>
-    <row r="42" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1582,66 +1760,84 @@
       <c r="K42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L42" s="3">
+        <v>0</v>
+      </c>
+      <c r="M42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>2111000</v>
+      </c>
+      <c r="E43" s="3">
+        <v>1935000</v>
+      </c>
+      <c r="F43" s="3">
         <v>1683000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>2182700</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>2055200</v>
       </c>
-      <c r="G43" s="3">
-        <v>1854200</v>
-      </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
+        <v>1689000</v>
+      </c>
+      <c r="J43" s="3">
         <v>2026900</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>2106100</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>2021400</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>1863200</v>
       </c>
     </row>
-    <row r="44" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>192000</v>
+      </c>
+      <c r="E44" s="3">
+        <v>180000</v>
+      </c>
+      <c r="F44" s="3">
         <v>159000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>155800</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>171800</v>
       </c>
-      <c r="G44" s="3">
-        <v>147200</v>
-      </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
+        <v>147000</v>
+      </c>
+      <c r="J44" s="3">
         <v>154000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>159900</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>178100</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>162000</v>
       </c>
     </row>
-    <row r="45" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -1669,42 +1865,54 @@
       <c r="K45" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="46" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M45" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="46" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>2573000</v>
+      </c>
+      <c r="E46" s="3">
+        <v>2232000</v>
+      </c>
+      <c r="F46" s="3">
         <v>2293000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>2378100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>2249900</v>
       </c>
-      <c r="G46" s="3">
-        <v>2022400</v>
-      </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
+        <v>2021000</v>
+      </c>
+      <c r="J46" s="3">
         <v>2206700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>2289700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>2216500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>2046000</v>
       </c>
     </row>
-    <row r="47" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3" t="s">
-        <v>8</v>
+      <c r="D47" s="3">
+        <v>32000</v>
       </c>
       <c r="E47" s="3" t="s">
         <v>8</v>
@@ -1712,8 +1920,8 @@
       <c r="F47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G47" s="3">
-        <v>31500</v>
+      <c r="G47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="H47" s="3" t="s">
         <v>8</v>
@@ -1724,69 +1932,87 @@
       <c r="J47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K47" s="3">
+      <c r="K47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M47" s="3">
         <v>57000</v>
       </c>
     </row>
-    <row r="48" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>4757000</v>
+      </c>
+      <c r="E48" s="3">
+        <v>4727000</v>
+      </c>
+      <c r="F48" s="3">
         <v>4695000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>4480300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>4478500</v>
       </c>
-      <c r="G48" s="3">
-        <v>4442300</v>
-      </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
+        <v>4561000</v>
+      </c>
+      <c r="J48" s="3">
         <v>4390200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>4420800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>4352400</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>4223300</v>
       </c>
     </row>
-    <row r="49" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>4161000</v>
+      </c>
+      <c r="E49" s="3">
+        <v>3814000</v>
+      </c>
+      <c r="F49" s="3">
         <v>3809000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>3694100</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>3662900</v>
       </c>
-      <c r="G49" s="3">
-        <v>3674700</v>
-      </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
+        <v>3781000</v>
+      </c>
+      <c r="J49" s="3">
         <v>3610300</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>3662000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>3702400</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>3697400</v>
       </c>
     </row>
-    <row r="50" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -1814,8 +2040,14 @@
       <c r="K50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L50" s="3">
+        <v>0</v>
+      </c>
+      <c r="M50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -1843,37 +2075,49 @@
       <c r="K51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L51" s="3">
+        <v>0</v>
+      </c>
+      <c r="M51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>12090000</v>
+      </c>
+      <c r="E52" s="3">
+        <v>11495000</v>
+      </c>
+      <c r="F52" s="3">
         <v>11516000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>11511300</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>11419600</v>
       </c>
-      <c r="G52" s="3">
-        <v>11520800</v>
-      </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
+        <v>11607000</v>
+      </c>
+      <c r="J52" s="3">
         <v>11725400</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>11936700</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>11886000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>11627600</v>
       </c>
     </row>
-    <row r="53" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -1901,37 +2145,49 @@
       <c r="K53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L53" s="3">
+        <v>0</v>
+      </c>
+      <c r="M53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>23613000</v>
+      </c>
+      <c r="E54" s="3">
+        <v>22268000</v>
+      </c>
+      <c r="F54" s="3">
         <v>22313000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>22063800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>21810900</v>
       </c>
-      <c r="G54" s="3">
-        <v>21691700</v>
-      </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
+        <v>21970000</v>
+      </c>
+      <c r="J54" s="3">
         <v>21932600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>22309200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>22157300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>21651300</v>
       </c>
     </row>
-    <row r="55" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -1943,8 +2199,10 @@
       <c r="I55" s="3"/>
       <c r="J55" s="3"/>
       <c r="K55" s="3"/>
-    </row>
-    <row r="56" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L55" s="3"/>
+      <c r="M55" s="3"/>
+    </row>
+    <row r="56" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -1956,66 +2214,80 @@
       <c r="I56" s="3"/>
       <c r="J56" s="3"/>
       <c r="K56" s="3"/>
-    </row>
-    <row r="57" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L56" s="3"/>
+      <c r="M56" s="3"/>
+    </row>
+    <row r="57" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>623000</v>
+      </c>
+      <c r="E57" s="3">
+        <v>472000</v>
+      </c>
+      <c r="F57" s="3">
         <v>383000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>1056100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>960600</v>
       </c>
-      <c r="G57" s="3">
-        <v>302500</v>
-      </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
+        <v>302000</v>
+      </c>
+      <c r="J57" s="3">
         <v>962000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>1011200</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>1004300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>521700</v>
       </c>
     </row>
-    <row r="58" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>845000</v>
+      </c>
+      <c r="E58" s="3">
+        <v>861000</v>
+      </c>
+      <c r="F58" s="3">
         <v>831000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>306900</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>303200</v>
       </c>
-      <c r="G58" s="3">
-        <v>298800</v>
-      </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
+        <v>273000</v>
+      </c>
+      <c r="J58" s="3">
         <v>288600</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>286600</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>284000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>273800</v>
       </c>
     </row>
-    <row r="59" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -2023,115 +2295,139 @@
         <v>8</v>
       </c>
       <c r="E59" s="3">
+        <v>207000</v>
+      </c>
+      <c r="F59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G59" s="3">
         <v>497700</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>418200</v>
       </c>
-      <c r="G59" s="3">
-        <v>81400</v>
-      </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
+        <v>176000</v>
+      </c>
+      <c r="J59" s="3">
         <v>279100</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>445300</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>599600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>78300</v>
       </c>
     </row>
-    <row r="60" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>2723000</v>
+      </c>
+      <c r="E60" s="3">
+        <v>2476000</v>
+      </c>
+      <c r="F60" s="3">
         <v>2252000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>1860700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>1682000</v>
       </c>
-      <c r="G60" s="3">
-        <v>1563300</v>
-      </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
+        <v>1559000</v>
+      </c>
+      <c r="J60" s="3">
         <v>1529700</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>1743100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>1887900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>1809300</v>
       </c>
     </row>
-    <row r="61" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>10578000</v>
+      </c>
+      <c r="E61" s="3">
+        <v>9757000</v>
+      </c>
+      <c r="F61" s="3">
         <v>9636000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>10279400</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>9987300</v>
       </c>
-      <c r="G61" s="3">
-        <v>10053400</v>
-      </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
+        <v>10103000</v>
+      </c>
+      <c r="J61" s="3">
         <v>10344500</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>10682400</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>10494000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>10401900</v>
       </c>
     </row>
-    <row r="62" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>402000</v>
+      </c>
+      <c r="E62" s="3">
+        <v>232000</v>
+      </c>
+      <c r="F62" s="3">
         <v>408000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>192500</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>183800</v>
       </c>
-      <c r="G62" s="3">
-        <v>166600</v>
-      </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
+        <v>221000</v>
+      </c>
+      <c r="J62" s="3">
         <v>147600</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>142800</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>138500</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>130900</v>
       </c>
     </row>
-    <row r="63" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2159,8 +2455,14 @@
       <c r="K63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L63" s="3">
+        <v>0</v>
+      </c>
+      <c r="M63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2188,8 +2490,14 @@
       <c r="K64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L64" s="3">
+        <v>0</v>
+      </c>
+      <c r="M64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2217,37 +2525,49 @@
       <c r="K65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L65" s="3">
+        <v>0</v>
+      </c>
+      <c r="M65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>16166000</v>
+      </c>
+      <c r="E66" s="3">
+        <v>14859000</v>
+      </c>
+      <c r="F66" s="3">
         <v>14698000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>14647300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>14122900</v>
       </c>
-      <c r="G66" s="3">
-        <v>14023600</v>
-      </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
+        <v>14171000</v>
+      </c>
+      <c r="J66" s="3">
         <v>14272800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>14811400</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>14762300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>14566700</v>
       </c>
     </row>
-    <row r="67" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2259,8 +2579,10 @@
       <c r="I67" s="3"/>
       <c r="J67" s="3"/>
       <c r="K67" s="3"/>
-    </row>
-    <row r="68" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L67" s="3"/>
+      <c r="M67" s="3"/>
+    </row>
+    <row r="68" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2288,8 +2610,14 @@
       <c r="K68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L68" s="3">
+        <v>0</v>
+      </c>
+      <c r="M68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2317,8 +2645,14 @@
       <c r="K69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L69" s="3">
+        <v>0</v>
+      </c>
+      <c r="M69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2346,8 +2680,14 @@
       <c r="K70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L70" s="3">
+        <v>0</v>
+      </c>
+      <c r="M70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2375,37 +2715,49 @@
       <c r="K71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L71" s="3">
+        <v>0</v>
+      </c>
+      <c r="M71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>7772000</v>
+      </c>
+      <c r="E72" s="3">
+        <v>7646000</v>
+      </c>
+      <c r="F72" s="3">
         <v>9895000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>9459600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>9327900</v>
       </c>
-      <c r="G72" s="3">
-        <v>8974200</v>
-      </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
+        <v>9103000</v>
+      </c>
+      <c r="J72" s="3">
         <v>8813500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>8497200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>8390100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>8102000</v>
       </c>
     </row>
-    <row r="73" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2433,8 +2785,14 @@
       <c r="K73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L73" s="3">
+        <v>0</v>
+      </c>
+      <c r="M73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2462,8 +2820,14 @@
       <c r="K74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L74" s="3">
+        <v>0</v>
+      </c>
+      <c r="M74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2491,37 +2855,49 @@
       <c r="K75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L75" s="3">
+        <v>0</v>
+      </c>
+      <c r="M75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>7447000</v>
+      </c>
+      <c r="E76" s="3">
+        <v>7409000</v>
+      </c>
+      <c r="F76" s="3">
         <v>7615000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>7416500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>7688000</v>
       </c>
-      <c r="G76" s="3">
-        <v>7668100</v>
-      </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
+        <v>7799000</v>
+      </c>
+      <c r="J76" s="3">
         <v>7659800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>7497800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>7395000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>7084600</v>
       </c>
     </row>
-    <row r="77" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2549,71 +2925,89 @@
       <c r="K77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L77" s="3">
+        <v>0</v>
+      </c>
+      <c r="M77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46234</v>
+      </c>
+      <c r="E80" s="2">
+        <v>46142</v>
+      </c>
+      <c r="F80" s="2">
         <v>46053</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45961</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45869</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45777</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45688</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45596</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45504</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45412</v>
       </c>
     </row>
-    <row r="81" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>438000</v>
+      </c>
+      <c r="E81" s="3">
+        <v>226000</v>
+      </c>
+      <c r="F81" s="3">
         <v>290000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>433500</v>
       </c>
-      <c r="F81" s="3">
-        <v>375500</v>
-      </c>
-      <c r="G81" s="3">
-        <v>311300</v>
-      </c>
       <c r="H81" s="3">
+        <v>373000</v>
+      </c>
+      <c r="I81" s="3">
+        <v>329000</v>
+      </c>
+      <c r="J81" s="3">
         <v>325000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>495500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>403500</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>324700</v>
       </c>
     </row>
-    <row r="82" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -2625,37 +3019,45 @@
       <c r="I82" s="3"/>
       <c r="J82" s="3"/>
       <c r="K82" s="3"/>
-    </row>
-    <row r="83" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L82" s="3"/>
+      <c r="M82" s="3"/>
+    </row>
+    <row r="83" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>113000</v>
+      </c>
+      <c r="E83" s="3">
+        <v>111000</v>
+      </c>
+      <c r="F83" s="3">
         <v>-888400</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>584800</v>
       </c>
-      <c r="F83" s="3">
+      <c r="H83" s="3">
         <v>570700</v>
       </c>
-      <c r="G83" s="3">
+      <c r="I83" s="3">
         <v>551300</v>
       </c>
-      <c r="H83" s="3">
+      <c r="J83" s="3">
         <v>546600</v>
       </c>
-      <c r="I83" s="3">
+      <c r="K83" s="3">
         <v>523700</v>
       </c>
-      <c r="J83" s="3">
+      <c r="L83" s="3">
         <v>496100</v>
       </c>
-      <c r="K83" s="3">
+      <c r="M83" s="3">
         <v>468600</v>
       </c>
     </row>
-    <row r="84" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -2683,8 +3085,14 @@
       <c r="K84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L84" s="3">
+        <v>0</v>
+      </c>
+      <c r="M84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -2712,8 +3120,14 @@
       <c r="K85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L85" s="3">
+        <v>0</v>
+      </c>
+      <c r="M85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -2741,8 +3155,14 @@
       <c r="K86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L86" s="3">
+        <v>0</v>
+      </c>
+      <c r="M86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -2770,8 +3190,14 @@
       <c r="K87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L87" s="3">
+        <v>0</v>
+      </c>
+      <c r="M87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -2799,37 +3225,49 @@
       <c r="K88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L88" s="3">
+        <v>0</v>
+      </c>
+      <c r="M88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>840000</v>
+      </c>
+      <c r="E89" s="3">
+        <v>950000</v>
+      </c>
+      <c r="F89" s="3">
         <v>1582600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>653900</v>
       </c>
-      <c r="F89" s="3">
-        <v>597500</v>
-      </c>
-      <c r="G89" s="3">
-        <v>982700</v>
-      </c>
       <c r="H89" s="3">
+        <v>868000</v>
+      </c>
+      <c r="I89" s="3">
+        <v>989000</v>
+      </c>
+      <c r="J89" s="3">
         <v>2159100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>408000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>287900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>844200</v>
       </c>
     </row>
-    <row r="90" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -2841,37 +3279,45 @@
       <c r="I90" s="3"/>
       <c r="J90" s="3"/>
       <c r="K90" s="3"/>
-    </row>
-    <row r="91" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L90" s="3"/>
+      <c r="M90" s="3"/>
+    </row>
+    <row r="91" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-1519400</v>
+        <v>-778000</v>
       </c>
       <c r="E91" s="3">
+        <v>-333000</v>
+      </c>
+      <c r="F91" s="3">
+        <v>-1237400</v>
+      </c>
+      <c r="G91" s="3">
         <v>-87400</v>
       </c>
-      <c r="F91" s="3">
-        <v>-112200</v>
-      </c>
-      <c r="G91" s="3">
-        <v>-76200</v>
-      </c>
       <c r="H91" s="3">
-        <v>-2116200</v>
+        <v>-413000</v>
       </c>
       <c r="I91" s="3">
+        <v>-112000</v>
+      </c>
+      <c r="J91" s="3">
+        <v>-1812200</v>
+      </c>
+      <c r="K91" s="3">
         <v>-167700</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-138100</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-165400</v>
       </c>
     </row>
-    <row r="92" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -2899,8 +3345,14 @@
       <c r="K92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L92" s="3">
+        <v>0</v>
+      </c>
+      <c r="M92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -2928,37 +3380,49 @@
       <c r="K93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L93" s="3">
+        <v>0</v>
+      </c>
+      <c r="M93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-1438000</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-384000</v>
+      </c>
+      <c r="F94" s="3">
         <v>-1257200</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-164500</v>
       </c>
-      <c r="F94" s="3">
-        <v>-119300</v>
-      </c>
-      <c r="G94" s="3">
-        <v>-139300</v>
-      </c>
       <c r="H94" s="3">
+        <v>-422000</v>
+      </c>
+      <c r="I94" s="3">
+        <v>-177000</v>
+      </c>
+      <c r="J94" s="3">
         <v>-1806300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-149100</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-185600</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-186000</v>
       </c>
     </row>
-    <row r="95" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -2970,37 +3434,45 @@
       <c r="I95" s="3"/>
       <c r="J95" s="3"/>
       <c r="K95" s="3"/>
-    </row>
-    <row r="96" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L95" s="3"/>
+      <c r="M95" s="3"/>
+    </row>
+    <row r="96" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3" t="s">
-        <v>8</v>
+      <c r="D96" s="3">
+        <v>307000</v>
       </c>
       <c r="E96" s="3">
+        <v>157000</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G96" s="3">
         <v>307300</v>
       </c>
-      <c r="F96" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G96" s="3">
-        <v>159200</v>
-      </c>
       <c r="H96" s="3" t="s">
         <v>8</v>
       </c>
       <c r="I96" s="3">
+        <v>157000</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K96" s="3">
         <v>387400</v>
       </c>
-      <c r="J96" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M96" s="3">
         <v>68900</v>
       </c>
     </row>
-    <row r="97" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3028,8 +3500,14 @@
       <c r="K97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L97" s="3">
+        <v>0</v>
+      </c>
+      <c r="M97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3057,8 +3535,14 @@
       <c r="K98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L98" s="3">
+        <v>0</v>
+      </c>
+      <c r="M98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3086,91 +3570,115 @@
       <c r="K99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L99" s="3">
+        <v>0</v>
+      </c>
+      <c r="M99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>601000</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-575000</v>
+      </c>
+      <c r="F100" s="3">
         <v>-327100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>-472600</v>
       </c>
-      <c r="F100" s="3">
-        <v>-476300</v>
-      </c>
-      <c r="G100" s="3">
-        <v>-849200</v>
-      </c>
       <c r="H100" s="3">
+        <v>-444000</v>
+      </c>
+      <c r="I100" s="3">
+        <v>-818000</v>
+      </c>
+      <c r="J100" s="3">
         <v>-349700</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>-252000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>-106300</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>-659500</v>
       </c>
     </row>
-    <row r="101" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
+      <c r="D101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E101" s="3">
+        <v>1000</v>
+      </c>
+      <c r="F101" s="3">
         <v>-1000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="G101" s="3">
         <v>-200</v>
       </c>
-      <c r="F101" s="3">
+      <c r="H101" s="3">
         <v>200</v>
       </c>
-      <c r="G101" s="3">
+      <c r="I101" s="3">
         <v>-300</v>
       </c>
-      <c r="H101" s="3">
+      <c r="J101" s="3">
         <v>600</v>
       </c>
-      <c r="I101" s="3">
+      <c r="K101" s="3">
         <v>-900</v>
       </c>
-      <c r="J101" s="3">
+      <c r="L101" s="3">
         <v>500</v>
       </c>
-      <c r="K101" s="3">
+      <c r="M101" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="102" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>3000</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-10000</v>
+      </c>
+      <c r="F102" s="3">
         <v>-600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>16700</v>
       </c>
-      <c r="F102" s="3">
-        <v>1900</v>
-      </c>
-      <c r="G102" s="3">
-        <v>-4800</v>
-      </c>
       <c r="H102" s="3">
+        <v>2000</v>
+      </c>
+      <c r="I102" s="3">
+        <v>-5000</v>
+      </c>
+      <c r="J102" s="3">
         <v>2100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>6700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-3800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>-1600</v>
       </c>
     </row>
